--- a/ig/main/ValueSet-jdv-j302-finess-statut-juridique-niv2-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j302-finess-statut-juridique-niv2-finess.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId6" sheetId="4"/>
+    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -125,6 +127,69 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260629120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>Etablissement Public</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>Etat et Collectivités Territoriales</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>Organisme Privé à But non Lucratif</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>Organisme Privé à Caractère Commercial</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>Personne Morale de Droit Etranger</t>
   </si>
 </sst>
 </file>
@@ -488,4 +553,176 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/main/ValueSet-jdv-j302-finess-statut-juridique-niv2-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j302-finess-statut-juridique-niv2-finess.xlsx
@@ -9,14 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Expansion Parameters" r:id="rId6" sheetId="4"/>
-    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -127,69 +125,6 @@
   </si>
   <si>
     <t>true</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>used-codesystem</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260629120000</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>Etablissement Public</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>Etat et Collectivités Territoriales</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>Organisme Privé à But non Lucratif</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>Organisme Privé à Caractère Commercial</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>Personne Morale de Droit Etranger</t>
   </si>
 </sst>
 </file>
@@ -553,176 +488,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>